--- a/小野町_引継ぎ_整理済/12_進捗管理/小野町_計画策定業務_進捗管理表_20260804.xlsx
+++ b/小野町_引継ぎ_整理済/12_進捗管理/小野町_計画策定業務_進捗管理表_20260804.xlsx
@@ -529,7 +529,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -670,7 +670,7 @@
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>成果品①③は初版作成済み。②は認定者推計の確定が前提</t>
+          <t>成果品①は第2版、③は第3版を作成済み。②は認定者推計の確定が前提</t>
         </is>
       </c>
     </row>
@@ -786,10 +786,10 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D10" s="3" t="n">
         <v>0</v>
@@ -801,16 +801,16 @@
         <v>0</v>
       </c>
       <c r="G10" s="7" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>33%</t>
+          <t>39%</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>見える化は取得完了。町資料は全項目が未受領</t>
+          <t>見える化は取得完了。第9期計画本文・第3期地域福祉計画本文を受領。実績データ系の町資料は未受領</t>
         </is>
       </c>
     </row>
@@ -856,10 +856,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D12" s="5" t="n">
         <v>15</v>
@@ -871,11 +871,11 @@
         <v>4</v>
       </c>
       <c r="G12" s="7" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>28%</t>
+          <t>30%</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr"/>
@@ -897,61 +897,68 @@
     <row r="17">
       <c r="A17" s="11" t="inlineStr">
         <is>
-          <t>見える化システムによる分析は12分野・135ファイルを取り込み、実質的に完了した。給付費等分析結果報告書（成果品①）と骨子案（成果品③）の初版を作成済み。</t>
+          <t>見える化システムによる分析は12分野・135ファイルを取り込み、実質的に完了した。給付費等分析結果報告書（成果品①）は第2版、高齢者計画の骨子案（成果品③）は第3版まで作成済み。</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="11" t="inlineStr">
         <is>
-          <t>一方、町からの実績データは全項目が未受領であり、サービス見込量推計・保険料算定・第9期評価の確定はいずれも着手できない。</t>
+          <t>第9期介護保険事業計画本文及び第3期地域福祉計画本文を受領し、前回計画の章構成・基本理念・3基本目標・14施策と、地域福祉計画との重複を確定させた。第9期の基本目標2の8施策のうち5施策が地域福祉計画と重複するため、成年後見制度の利用促進は移管、高齢者虐待防止・災害対応・地域の支え合いは連携として整理した。</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="11" t="inlineStr">
         <is>
-          <t>障がい計画は、委託仕様が定める関係者団体等ヒアリングが未着手であり、調査票も児童用に本文欠落が残る。工程上、8月中の調査票確定が必要。</t>
+          <t>一方、町からの実績データは全項目が未受領であり、サービス見込量推計・保険料算定・第9期評価の確定はいずれも着手できない。</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="11" t="inlineStr">
         <is>
+          <t>障がい計画は、委託仕様が定める関係者団体等ヒアリングが未着手であり、調査票も児童用に本文欠落が残る。工程上、8月中の調査票確定が必要。</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="11" t="inlineStr">
+        <is>
           <t>委託仕様書の工程（障がい：調査は7月まで、骨子案9月、骨子案検討10月）から3〜4か月遅延している。工程変更について町との協議・記録化が必要（仕様書8①・11④）。</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="10" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="10" t="inlineStr">
         <is>
           <t>■ 直近のマイルストーン</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>令和8年8月19日　小野町自立支援協議会（第1回）　※資料第3版を作成済み</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>令和8年8月中　　障がい者ニーズ調査の調査票確定（児童用の本文復元が前提）</t>
+          <t>令和8年8月19日　小野町自立支援協議会（第1回）　※資料第3版を作成済み</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>令和8年9〜10月　障がい者ニーズ調査の発送・回収、関係者団体等ヒアリング</t>
+          <t>令和8年8月中　　障がい者ニーズ調査の調査票確定（児童用の本文復元が前提）</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
+        <is>
+          <t>令和8年9〜10月　障がい者ニーズ調査の発送・回収、関係者団体等ヒアリング</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
         <is>
           <t>令和8年12月頃　 自立支援協議会（第2回）：調査結果・骨子案・見込量の考え方</t>
         </is>
@@ -1188,7 +1195,7 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>介護保険給付費等分析結果報告書（8章・表32）</t>
+          <t>介護保険給付費等分析結果報告書 第2版（8章・表37）。第7章7に第9期の見込みとの対比を追加</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
@@ -1299,7 +1306,7 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>骨子案第6章で4ケース（標準・施設整備・制度改正・基金活用）を設定</t>
+          <t>第9期の算定根拠（標準給付費3年計3,566,486千円、基金取崩35,000千円、所得段階別保険料率）を確認済み。第10期はこれを基礎に算定する</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
@@ -1341,7 +1348,7 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>令和6・7年度の決算で補完。基金残高の実額を確認</t>
+          <t>令和6・7年度の決算で補完。第9期が見込んだ基金取崩3,500万円の実施状況と基金残高の実額を確認</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
@@ -1373,7 +1380,7 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>高齢者計画 骨子案（7章＋資料編、データ待ち10箇所）</t>
+          <t>高齢者計画 骨子案 第3版。第9期の5章構成・3基本目標・14施策を反映し、地域福祉計画との重複を精査済み</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
@@ -1383,7 +1390,7 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>第9期計画本文が未入手</t>
+          <t>―</t>
         </is>
       </c>
     </row>
@@ -1575,7 +1582,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>初版作成済み（8章・表32・約17,500字）。見える化データに基づく分析は完了</t>
+          <t>第2版作成済み（8章・表37・約24,300字）。見える化データに基づく分析は完了。第9期計画との対比、施策体系（3基本目標14施策）との対応まで整理済み</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
@@ -1639,12 +1646,12 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>初版作成済み（7章＋資料編）。章立て・施策体系・基本目標5案・保険料4ケースを設定</t>
+          <t>第3版作成済み（第9期の5章構成を継承）。基本理念・3基本目標・14施策への対応、地域福祉計画との役割分担、第9期の見込み実績対比まで整理済み</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>第9期計画本文、実績データ、協議会での合意</t>
+          <t>実績データ、協議会での合意</t>
         </is>
       </c>
     </row>
@@ -2749,7 +2756,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3120,7 +3127,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>第9期高齢者保健福祉計画・介護保険事業計画 本文</t>
+          <t>第9期高齢者保健福祉計画・介護保険事業計画 本文（令和6年3月）</t>
         </is>
       </c>
       <c r="C12" s="13" t="inlineStr">
@@ -3128,19 +3135,19 @@
           <t>町</t>
         </is>
       </c>
-      <c r="D12" s="16" t="inlineStr">
-        <is>
-          <t>未着手</t>
+      <c r="D12" s="14" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="E12" s="13" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>第9期評価の確定に必須</t>
+          <t>5章構成・基本理念・3基本目標・14施策、標準給付費見込3,566,486千円、基金取崩35,000千円、保険料6,600円の算定根拠を確認。骨子案第3版・成果品①第2版に反映済み</t>
         </is>
       </c>
     </row>
@@ -3152,7 +3159,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>令和3〜7年度 認定者数（要介護度別・年齢階層別）の実数</t>
+          <t>第3期地域福祉計画 本文・概要版（令和8年3月）</t>
         </is>
       </c>
       <c r="C13" s="13" t="inlineStr">
@@ -3160,19 +3167,19 @@
           <t>町</t>
         </is>
       </c>
-      <c r="D13" s="16" t="inlineStr">
-        <is>
-          <t>未着手</t>
+      <c r="D13" s="14" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="E13" s="13" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>最優先。県内唯一の異常値の検証</t>
+          <t>3基本目標。第5章に第1期成年後見制度利用促進基本計画を一体策定。第9期高齢者計画との重複5施策を特定し役割分担を整理済み</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3191,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>認定審査・更新認定の運用変更の有無</t>
+          <t>令和3〜7年度 認定者数（要介護度別・年齢階層別）の実数</t>
         </is>
       </c>
       <c r="C14" s="13" t="inlineStr">
@@ -3204,7 +3211,7 @@
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>同上</t>
+          <t>最優先。県内唯一の異常値の検証</t>
         </is>
       </c>
     </row>
@@ -3216,7 +3223,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>令和3〜8年度 サービス別給付費・利用者数</t>
+          <t>認定審査・更新認定の運用変更の有無</t>
         </is>
       </c>
       <c r="C15" s="13" t="inlineStr">
@@ -3236,7 +3243,7 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>見える化との突合</t>
+          <t>同上</t>
         </is>
       </c>
     </row>
@@ -3248,7 +3255,7 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>令和7年度 ニーズ調査・在宅介護実態調査の結果</t>
+          <t>令和3〜8年度 サービス別給付費・利用者数</t>
         </is>
       </c>
       <c r="C16" s="13" t="inlineStr">
@@ -3268,7 +3275,7 @@
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>仕様書4(1)③が反映を求める</t>
+          <t>見える化との突合</t>
         </is>
       </c>
     </row>
@@ -3280,7 +3287,7 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>介護給付費準備基金の残高と取崩方針</t>
+          <t>令和7年度 ニーズ調査・在宅介護実態調査の結果</t>
         </is>
       </c>
       <c r="C17" s="13" t="inlineStr">
@@ -3300,7 +3307,7 @@
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>保険料算定に必須</t>
+          <t>仕様書4(1)③が反映を求める</t>
         </is>
       </c>
     </row>
@@ -3312,7 +3319,7 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>所得段階別第1号被保険者数</t>
+          <t>介護給付費準備基金の残高と取崩方針</t>
         </is>
       </c>
       <c r="C18" s="13" t="inlineStr">
@@ -3332,7 +3339,7 @@
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>同上</t>
+          <t>保険料算定に必須</t>
         </is>
       </c>
     </row>
@@ -3344,7 +3351,7 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>地域支援事業費の実績と事業別内訳</t>
+          <t>所得段階別第1号被保険者数</t>
         </is>
       </c>
       <c r="C19" s="13" t="inlineStr">
@@ -3376,7 +3383,7 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>総合事業・通いの場の事業実績（令和3〜7年度）</t>
+          <t>地域支援事業費の実績と事業別内訳</t>
         </is>
       </c>
       <c r="C20" s="13" t="inlineStr">
@@ -3396,7 +3403,7 @@
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>見える化に令和3年度以降がないため代替が必要</t>
+          <t>同上</t>
         </is>
       </c>
     </row>
@@ -3408,7 +3415,7 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>事業所別定員・稼働率・町内外利用・待機・休廃止</t>
+          <t>総合事業・通いの場の事業実績（令和3〜7年度）</t>
         </is>
       </c>
       <c r="C21" s="13" t="inlineStr">
@@ -3428,7 +3435,7 @@
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>供給制約の確認</t>
+          <t>見える化に令和3年度以降がないため代替が必要</t>
         </is>
       </c>
     </row>
@@ -3440,7 +3447,7 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>居宅介護支援事業所の担当件数・受付状況</t>
+          <t>事業所別定員・稼働率・町内外利用・待機・休廃止</t>
         </is>
       </c>
       <c r="C22" s="13" t="inlineStr">
@@ -3460,7 +3467,7 @@
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>事業所5→3の減少と在宅利用低下の関係</t>
+          <t>供給制約の確認</t>
         </is>
       </c>
     </row>
@@ -3472,12 +3479,12 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>認知症施策の実績（研修、初期集中支援チーム等）</t>
+          <t>居宅介護支援事業所の担当件数・受付状況</t>
         </is>
       </c>
       <c r="C23" s="13" t="inlineStr">
         <is>
-          <t>町・県</t>
+          <t>町</t>
         </is>
       </c>
       <c r="D23" s="16" t="inlineStr">
@@ -3492,7 +3499,7 @@
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>見える化では把握できない</t>
+          <t>事業所5→3の減少と在宅利用低下の関係</t>
         </is>
       </c>
     </row>
@@ -3504,12 +3511,12 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>障がい：令和6〜8年度 サービス別実績、支給決定量、町内外事業所別利用</t>
+          <t>認知症施策の実績（研修、初期集中支援チーム等）</t>
         </is>
       </c>
       <c r="C24" s="13" t="inlineStr">
         <is>
-          <t>町</t>
+          <t>町・県</t>
         </is>
       </c>
       <c r="D24" s="16" t="inlineStr">
@@ -3524,7 +3531,7 @@
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>見込量算定に必須</t>
+          <t>見える化では把握できない</t>
         </is>
       </c>
     </row>
@@ -3536,7 +3543,7 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>障がい：セルフプラン件数、相談支援専門員数</t>
+          <t>障がい：令和6〜8年度 サービス別実績、支給決定量、町内外事業所別利用</t>
         </is>
       </c>
       <c r="C25" s="13" t="inlineStr">
@@ -3556,7 +3563,7 @@
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>国の新規成果目標「望まないセルフプランゼロ」の起点</t>
+          <t>見込量算定に必須</t>
         </is>
       </c>
     </row>
@@ -3568,7 +3575,7 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>障がい：特別支援学校卒業予定者、医療的ケア児の状況</t>
+          <t>障がい：セルフプラン件数、相談支援専門員数</t>
         </is>
       </c>
       <c r="C26" s="13" t="inlineStr">
@@ -3588,24 +3595,24 @@
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>18歳移行の見込量</t>
+          <t>国の新規成果目標「望まないセルフプランゼロ」の起点</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="13" t="inlineStr">
         <is>
-          <t>その他</t>
+          <t>町資料</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>★0727版アンケート調査票（一般用・児童用）</t>
+          <t>障がい：特別支援学校卒業予定者、医療的ケア児の状況</t>
         </is>
       </c>
       <c r="C27" s="13" t="inlineStr">
         <is>
-          <t>町・他メンバー</t>
+          <t>町</t>
         </is>
       </c>
       <c r="D27" s="16" t="inlineStr">
@@ -3620,7 +3627,7 @@
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>本文復元の対象ファイル。手元にない</t>
+          <t>18歳移行の見込量</t>
         </is>
       </c>
     </row>
@@ -3632,25 +3639,57 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
+          <t>★0727版アンケート調査票（一般用・児童用）</t>
+        </is>
+      </c>
+      <c r="C28" s="13" t="inlineStr">
+        <is>
+          <t>町・他メンバー</t>
+        </is>
+      </c>
+      <c r="D28" s="16" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="E28" s="13" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>本文復元の対象ファイル。手元にない</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="13" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
           <t>打合せ記録（契約後）</t>
         </is>
       </c>
-      <c r="C28" s="13" t="inlineStr">
+      <c r="C29" s="13" t="inlineStr">
         <is>
           <t>受託者作成・町確認</t>
         </is>
       </c>
-      <c r="D28" s="16" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="E28" s="13" t="inlineStr">
+      <c r="D29" s="16" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="E29" s="13" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="F28" s="3" t="inlineStr">
+      <c r="F29" s="3" t="inlineStr">
         <is>
           <t>仕様書8①により受託者が作成し相互確認する義務</t>
         </is>

--- a/小野町_引継ぎ_整理済/12_進捗管理/小野町_計画策定業務_進捗管理表_20260804.xlsx
+++ b/小野町_引継ぎ_整理済/12_進捗管理/小野町_計画策定業務_進捗管理表_20260804.xlsx
@@ -529,7 +529,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I27"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -617,7 +617,7 @@
         <v>3</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E5" s="3" t="n">
         <v>0</v>
@@ -626,11 +626,11 @@
         <v>3</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>37%</t>
+          <t>40%</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
@@ -794,18 +794,18 @@
       <c r="D10" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E10" s="3" t="n">
-        <v>0</v>
+      <c r="E10" s="8" t="n">
+        <v>1</v>
       </c>
       <c r="F10" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G10" s="7" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>39%</t>
+          <t>40%</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
@@ -862,20 +862,20 @@
         <v>16</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E12" s="8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F12" s="6" t="n">
         <v>4</v>
       </c>
       <c r="G12" s="7" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>30%</t>
+          <t>31%</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr"/>
@@ -918,47 +918,61 @@
     <row r="20">
       <c r="A20" s="11" t="inlineStr">
         <is>
-          <t>障がい計画は、委託仕様が定める関係者団体等ヒアリングが未着手であり、調査票も児童用に本文欠落が残る。工程上、8月中の調査票確定が必要。</t>
+          <t>令和7年度調査（ニーズ調査・在宅介護実態調査）は紙の集計表のみを受領しており、電子データが未受領である。個票または年齢階層別・要介護度別のクロス集計がないと、計画書第2章の作成と施策の根拠づけができない。協議会資料 第2部で必要なデータを提示済み。</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="11" t="inlineStr">
         <is>
+          <t>障がい計画は、委託仕様が定める関係者団体等ヒアリングが未着手であり、調査票も児童用に本文欠落が残る。工程上、8月中の調査票確定が必要。</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="11" t="inlineStr">
+        <is>
           <t>委託仕様書の工程（障がい：調査は7月まで、骨子案9月、骨子案検討10月）から3〜4か月遅延している。工程変更について町との協議・記録化が必要（仕様書8①・11④）。</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="10" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="10" t="inlineStr">
         <is>
           <t>■ 直近のマイルストーン</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>令和8年8月19日　小野町自立支援協議会（第1回）　※資料第3版を作成済み</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>令和8年8月中　　障がい者ニーズ調査の調査票確定（児童用の本文復元が前提）</t>
+          <t>令和8年8月19日　小野町自立支援協議会（第1回）　※資料第3版を作成済み</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>令和8年9〜10月　障がい者ニーズ調査の発送・回収、関係者団体等ヒアリング</t>
+          <t>令和8年8〜9月　　高齢者福祉サービス推進協議会：第9期評価・調査結果　※資料作成済み、開催日未定</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
+        <is>
+          <t>令和8年8月中　　障がい者ニーズ調査の調査票確定（児童用の本文復元が前提）</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>令和8年9〜10月　障がい者ニーズ調査の発送・回収、関係者団体等ヒアリング</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
         <is>
           <t>令和8年12月頃　 自立支援協議会（第2回）：調査結果・骨子案・見込量の考え方</t>
         </is>
@@ -1232,17 +1246,17 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>**紙の集計表のみ受領。電子データが未受領。** 協議会資料 第2部に、前回調査（R4・R5）の値を比較基準として整理し、確認事項・必要データ・集計設計を提示済み</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>町から単純集計・クロス集計・自由記述を受領。見える化のE系・Z系が登録されていれば併せて取得</t>
+          <t>個票データ（または年齢階層別・要介護度別クロス集計）、調査票、配布数・回収数・実施時期を受領。見える化のE系・Z系が登録されていれば併せて取得</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>調査結果が未受領</t>
+          <t>電子データが未受領</t>
         </is>
       </c>
     </row>
@@ -1484,19 +1498,19 @@
           <t>小野町高齢者福祉サービス推進協議会の開催支援、パブコメ支援</t>
         </is>
       </c>
-      <c r="D14" s="16" t="inlineStr">
-        <is>
-          <t>未着手</t>
+      <c r="D14" s="17" t="inlineStr">
+        <is>
+          <t>進行中</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>協議会資料「第9期計画の評価及び令和7年度調査結果の整理」を作成済み（3部構成・30表）。第9期計画が定める4つの点検項目に沿って評価</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>協議会の開催回数・時期を町と確定する</t>
+          <t>協議会の開催回数・時期を町と確定する。パブコメの実施時期も併せて確定</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
@@ -3295,19 +3309,19 @@
           <t>町</t>
         </is>
       </c>
-      <c r="D17" s="16" t="inlineStr">
-        <is>
-          <t>未着手</t>
+      <c r="D17" s="18" t="inlineStr">
+        <is>
+          <t>要対応</t>
         </is>
       </c>
       <c r="E17" s="13" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>紙のみ受領</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>仕様書4(1)③が反映を求める</t>
+          <t>**紙の集計表のみ受領、電子データが未受領。** 個票（またはクロス集計表）・調査票・配布数/回収数/実施時期が必要。仕様書4(1)③が反映を求める</t>
         </is>
       </c>
     </row>
